--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -484,12 +484,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,7 +715,91 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 19:19:09</t>
+          <t>2026-08-16 14:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REC-20260816-GHCLTEXTIL-2DFFCD</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>GHCL Textiles Limited</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>119.69</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>141.64</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>154.97</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1275</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>152604.75</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="7" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-1963.5</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 14:08:09</t>
         </is>
       </c>
     </row>

--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -484,12 +484,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,7 +715,175 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 19:19:09</t>
+          <t>2026-08-16 19:50:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>REC-20260816-UBL-4BC2FA</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>United Breweries Limited</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1376.6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1394.51</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>1306.54</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1552.86</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1640.83</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>1790.38</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>157579.63</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>1376.6</v>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" s="7" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-2023.83</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 19:50:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>REC-20260816-ABBOTINDIA-D586CC</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Abbott India Limited</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>27060</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>27412.1</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>25546</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>30771.08</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32637.18</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>35809.55</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>137060.5</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>27060</v>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="7" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-1760.5</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 19:50:48</t>
         </is>
       </c>
     </row>

--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,14 +715,14 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 19:50:48</t>
+          <t>2026-08-16 14:08:09</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>REC-20260816-UBL-4BC2FA</t>
+          <t>REC-20260816-GHCLTEXTIL-2DFFCD</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>United Breweries Limited</t>
+          <t>GHCL Textiles Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -754,31 +754,31 @@
         <v>83.8</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1376.6</v>
+        <v>118.15</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>1394.51</v>
+        <v>119.69</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1306.54</v>
+        <v>111.85</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1552.86</v>
+        <v>133.8</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1640.83</v>
+        <v>141.64</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1790.38</v>
+        <v>154.97</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>113</v>
+        <v>1275</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>157579.63</v>
+        <v>152604.75</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>1376.6</v>
+        <v>118.15</v>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
@@ -786,104 +786,20 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-2023.83</v>
+        <v>-1963.5</v>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 19:50:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>REC-20260816-ABBOTINDIA-D586CC</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ABBOTINDIA</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Abbott India Limited</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>27060</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>27412.1</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>25546</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>30771.08</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>32637.18</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>35809.55</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>137060.5</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>27060</v>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="7" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>-1760.5</v>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16 19:50:48</t>
+          <t>2026-08-16 14:08:09</t>
         </is>
       </c>
     </row>

--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -484,13 +484,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,7 +715,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:08:09</t>
+          <t>2026-08-16 14:24:08</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" s="7" t="n">
         <v>-1.29</v>
@@ -799,7 +799,91 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:08:09</t>
+          <t>2026-08-16 14:24:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>REC-20260816-ABCAPITAL-38D2EE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Birla Capital Limited</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>406.22</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>456.03</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>483.7</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>530.74</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>146645.42</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="7" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-1884.42</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 14:24:08</t>
         </is>
       </c>
     </row>

--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,7 +715,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:24:08</t>
+          <t>2026-08-16 14:25:39</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" s="7" t="n">
         <v>-1.29</v>
@@ -799,7 +799,7 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:24:08</t>
+          <t>2026-08-16 14:25:39</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" s="7" t="n">
         <v>-1.29</v>
@@ -883,7 +883,91 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:24:08</t>
+          <t>2026-08-16 14:25:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>REC-20260816-ABCAPITAL-5354CE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Birla Capital Limited</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>406.22</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>456.03</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>483.7</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>530.74</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>146645.42</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-1884.42</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 14:25:39</t>
         </is>
       </c>
     </row>

--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,7 +715,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:25:39</t>
+          <t>2026-08-16 14:29:06</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S3" s="7" t="n">
         <v>-1.29</v>
@@ -799,7 +799,7 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:25:39</t>
+          <t>2026-08-16 14:29:06</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" s="7" t="n">
         <v>-1.29</v>
@@ -883,7 +883,7 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:25:39</t>
+          <t>2026-08-16 14:29:06</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" s="7" t="n">
         <v>-1.29</v>
@@ -967,7 +967,91 @@
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:25:39</t>
+          <t>2026-08-16 14:29:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>REC-20260816-ABCAPITAL-98E323</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Birla Capital Limited</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>406.22</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>456.03</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>483.7</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>530.74</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>361</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>146645.42</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-1884.42</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 14:29:06</t>
         </is>
       </c>
     </row>

--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,7 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="19" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,7 +715,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:29:06</t>
+          <t>2026-08-16 15:04:27</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S3" s="7" t="n">
         <v>-1.29</v>
@@ -799,7 +799,7 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:29:06</t>
+          <t>2026-08-16 15:04:27</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4" s="7" t="n">
         <v>-1.29</v>
@@ -883,7 +883,7 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:29:06</t>
+          <t>2026-08-16 15:04:27</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S5" s="7" t="n">
         <v>-1.29</v>
@@ -967,7 +967,7 @@
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:29:06</t>
+          <t>2026-08-16 15:04:27</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" s="7" t="n">
         <v>-1.29</v>
@@ -1051,7 +1051,91 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 14:29:06</t>
+          <t>2026-08-16 15:04:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>REC-20260816-JSWCEMENT-FC3E63</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>JSWCEMENT</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>JSW Cement Limited</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>130.02</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>131.71</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>123.62</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>146.27</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>154.36</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>168.12</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1236</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>162793.56</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>130.02</v>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>PENDING_ENTRY</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 15:04:27</t>
         </is>
       </c>
     </row>

--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,7 +715,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 15:04:27</t>
+          <t>2026-08-16 17:41:14</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S3" s="7" t="n">
         <v>-1.29</v>
@@ -799,7 +799,7 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 15:04:27</t>
+          <t>2026-08-16 17:41:14</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S4" s="7" t="n">
         <v>-1.29</v>
@@ -883,7 +883,7 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 15:04:27</t>
+          <t>2026-08-16 17:41:14</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" s="7" t="n">
         <v>-1.29</v>
@@ -967,7 +967,7 @@
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 15:04:27</t>
+          <t>2026-08-16 17:41:14</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S6" s="7" t="n">
         <v>-1.29</v>
@@ -1051,7 +1051,7 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 15:04:27</t>
+          <t>2026-08-16 17:41:14</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 15:04:27</t>
+          <t>2026-08-16 17:41:14</t>
         </is>
       </c>
     </row>

--- a/data/trade_ledger.xlsx
+++ b/data/trade_ledger.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S2" s="7" t="n">
         <v>-1.28</v>
@@ -715,7 +715,7 @@
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 17:41:14</t>
+          <t>2026-08-16 17:50:09</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S3" s="7" t="n">
         <v>-1.29</v>
@@ -799,7 +799,7 @@
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 17:41:14</t>
+          <t>2026-08-16 17:50:09</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S4" s="7" t="n">
         <v>-1.29</v>
@@ -883,7 +883,7 @@
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 17:41:14</t>
+          <t>2026-08-16 17:50:09</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S5" s="7" t="n">
         <v>-1.29</v>
@@ -967,7 +967,7 @@
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 17:41:14</t>
+          <t>2026-08-16 17:50:09</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" s="7" t="n">
         <v>-1.29</v>
@@ -1051,7 +1051,7 @@
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 17:41:14</t>
+          <t>2026-08-16 17:50:09</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>0</v>
@@ -1135,7 +1135,91 @@
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16 17:41:14</t>
+          <t>2026-08-16 17:50:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>REC-20260816-CASTROLIND-F78222</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Castrol India Limited</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>186.82</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>188.98</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>178.21</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>208.09</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>218.76</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>236.89</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>937</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>176980.56</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>186.82</v>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>PENDING_ENTRY</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16 17:50:09</t>
         </is>
       </c>
     </row>
